--- a/pensum/ok01/OK01_Tema_Regneark_Startbudsjett.xlsx
+++ b/pensum/ok01/OK01_Tema_Regneark_Startbudsjett.xlsx
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +133,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="true" numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -687,7 +693,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row ht="24.75" customHeight="true" r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Servicebil</t>
@@ -836,7 +842,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18">
+    <row ht="24.75" customHeight="true" r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Kundefordringer</t>
@@ -914,7 +920,7 @@
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
     </row>
-    <row r="26">
+    <row ht="24.75" customHeight="true" r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Egenkapital, andel av kapitalbehovet</t>
@@ -956,7 +962,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row ht="24.75" customHeight="true" r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Kassekreditt og offentlige avgifter</t>
@@ -1195,7 +1201,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row ht="24.75" customHeight="true" r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Sosiale kostnader, andel av lønn</t>
@@ -1437,7 +1443,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="41">
+    <row ht="24.75" customHeight="true" r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Rente kassekreditt, sats</t>
@@ -1463,7 +1469,7 @@
         <v/>
       </c>
     </row>
-    <row r="43">
+    <row ht="24.75" customHeight="true" r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Resultat før skatt</t>
@@ -1489,8 +1495,8 @@
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="n"/>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row ht="27" customHeight="true" r="46">
+      <c s="22" r="A46" t="inlineStr">
         <is>
           <t>Faste kostnader (lønn, andre driftskostnader, avskrivninger, renter)</t>
         </is>
@@ -1505,8 +1511,8 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+    <row ht="27" customHeight="true" r="47">
+      <c s="21" r="A47" t="inlineStr">
         <is>
           <t>Nullpunktomsetning = faste kostnader / bruttofortjenesteandel</t>
         </is>
@@ -1521,7 +1527,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row ht="24.75" customHeight="true" r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>Avstand til nullpunktet</t>
@@ -1671,7 +1677,7 @@
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row ht="92.25" customHeight="true" r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Andel av kredittsalget betalt samme måned</t>
@@ -1686,7 +1692,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row ht="69.75" customHeight="true" r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Varekjøp, andel av salget (ekskl. mva)</t>
@@ -1701,7 +1707,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row ht="92.25" customHeight="true" r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Andel av varekjøpet betalt samme måned</t>
@@ -1716,7 +1722,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row ht="58.5" customHeight="true" r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Arbeidsgiveravgift</t>
@@ -1731,8 +1737,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row ht="126" customHeight="true" r="10">
+      <c s="22" r="A10" t="inlineStr">
         <is>
           <t>Pensjon (OTP) og personalforsikring, andel av lønn</t>
         </is>
@@ -1746,7 +1752,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row ht="81" customHeight="true" r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Merverdiavgift</t>
@@ -1761,7 +1767,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row ht="58.5" customHeight="true" r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Kassekredittramme</t>
@@ -1776,7 +1782,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row ht="24.75" customHeight="true" r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Avdrag på lån per kvartal (fra 2. kvartal)</t>
@@ -1792,7 +1798,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row ht="58.5" customHeight="true" r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Rente på lån per kvartal</t>
@@ -1896,7 +1902,7 @@
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
     </row>
-    <row r="18">
+    <row ht="24.75" customHeight="true" r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Salg ekskl. mva (budsjett)</t>
@@ -2088,7 +2094,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row ht="24.75" customHeight="true" r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Innbetaling fra kredittkunder</t>
@@ -2253,7 +2259,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row ht="24.75" customHeight="true" r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Mva til gode (refusjon)</t>
@@ -2499,7 +2505,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row ht="24.75" customHeight="true" r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Betalt til grossist</t>
@@ -2808,7 +2814,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row ht="24.75" customHeight="true" r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Avdrag på lån</t>
@@ -2914,7 +2920,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row ht="24.75" customHeight="true" r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Mva innbetalt</t>
@@ -2978,7 +2984,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row ht="24.75" customHeight="true" r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Sum utbetalinger</t>
@@ -3226,7 +3232,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row ht="24.75" customHeight="true" r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>Ledig på kassekreditten</t>
@@ -3415,8 +3421,8 @@
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+    <row ht="27" customHeight="true" r="52">
+      <c s="22" r="A52" t="inlineStr">
         <is>
           <t>Mva å betale (+) eller få igjen (−) for terminen, forfall</t>
         </is>
@@ -3479,7 +3485,7 @@
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
     </row>
-    <row r="55">
+    <row ht="69.75" customHeight="true" r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
           <t>Laveste beholdning i året</t>
@@ -3506,7 +3512,7 @@
         <v/>
       </c>
     </row>
-    <row r="57">
+    <row ht="69.75" customHeight="true" r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>Beholdning 31. desember</t>
@@ -3533,8 +3539,8 @@
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+    <row ht="204.75" customHeight="true" r="59">
+      <c s="21" r="A59" t="inlineStr">
         <is>
           <t>Forskjell: penger som tilhører andre eller kommer senere</t>
         </is>
@@ -3567,21 +3573,21 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row ht="17.25" customHeight="true" r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
           <t>Sett kassekredittrammen (B12) til 0. Hvilken måned går det galt, og hvor mye mangler?</t>
         </is>
       </c>
     </row>
-    <row r="65">
+    <row ht="17.25" customHeight="true" r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
           <t>Flytt 200 000 av salget fra november til januar (rad 18). Hva skjer med bunnen?</t>
         </is>
       </c>
     </row>
-    <row r="66">
+    <row ht="17.25" customHeight="true" r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
           <t>Sett andelen kredittsalg (arket Kapitalbehov, B16) til 60 % — slik det ble da Nordlys begynte å jobbe for entreprenører. Se hva det gjør med januar og februar.</t>
@@ -3778,7 +3784,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row ht="24.75" customHeight="true" r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Egenkapital du kan skyte inn</t>
@@ -3889,8 +3895,8 @@
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row ht="27" customHeight="true" r="29">
+      <c s="22" r="A29" t="inlineStr">
         <is>
           <t>Andre driftskostnader (husleie, forsikring, regnskap, bil, telefon …)</t>
         </is>
